--- a/Data/Bronze/MCIC.INVESTIGACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 4. EGRESADOS/e. Caracterización e impacto de los egresados/F4_Egresados_Impacto_Investigacion.xlsx
+++ b/Data/Bronze/MCIC.INVESTIGACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 4. EGRESADOS/e. Caracterización e impacto de los egresados/F4_Egresados_Impacto_Investigacion.xlsx
@@ -683,7 +683,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">

--- a/Data/Bronze/MCIC.INVESTIGACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 4. EGRESADOS/e. Caracterización e impacto de los egresados/F4_Egresados_Impacto_Investigacion.xlsx
+++ b/Data/Bronze/MCIC.INVESTIGACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 4. EGRESADOS/e. Caracterización e impacto de los egresados/F4_Egresados_Impacto_Investigacion.xlsx
@@ -715,16 +715,16 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>91 %</t>
+          <t>92 %</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>91 %</t>
+          <t>92 %</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -1296,7 +1296,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>11 respuestas de egresados de Investigación. Sin nombres, documentos ni organizaciones; el texto libre no se publica.</t>
+          <t>13 respuestas de egresados de Investigación. Sin nombres, documentos ni organizaciones; el texto libre no se publica.</t>
         </is>
       </c>
     </row>
@@ -1335,29 +1335,29 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>9 %</t>
+          <t>8 %</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>18 %</t>
+          <t>8 %</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
@@ -1365,14 +1365,14 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>18 %</t>
+          <t>15 %</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
@@ -1380,1643 +1380,1673 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>18 %</t>
+          <t>15 %</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>27 %</t>
+          <t>15 %</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>23 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>15 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Énfasis</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Ingeniería de Software</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>69 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Geomática</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>15 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Teleinformática</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>15 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Grupo de investigación del trabajo de grado</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>INTECSE</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>31 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>GIIRA</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>23 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>INTERNET INTELIGENTE</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>15 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>GICOGE</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>9 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Énfasis</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>8 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>GITEM++</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>8 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>PROPROBOS</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>8 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>GCEM</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>8 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Situación principal actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Respuesta</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>Egresados</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Ingeniería de Software</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Docente</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>38 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>Empleado(a)</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>38 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Independiente/consultor(a)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>15 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Estudiante</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>8 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Sector en el que se desempeña</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Educación Superior</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>64 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Geomática</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="n">
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>54 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>Gobierno/sector público</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>23 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>TIC</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>8 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>8 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Industria</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>8 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Nivel de responsabilidad del cargo</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Docencia</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>38 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>Profesional/especialista</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>31 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Coordinación</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>18 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Teleinformática</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>15 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>Dirección/jefatura</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>8 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Investigación</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>8 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Relación de la actividad actual con la formación recibida</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Totalmente Relacionada</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>54 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>Muy Relacionada</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>23 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Parcialmente relacionada</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>18 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Grupo de investigación del trabajo de grado</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>15 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>Poco relacionada</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>8 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Aporte de la MCIC a su desarrollo (número de egresados por nivel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>Dimensión</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>Muy alto</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>Ningún aporte</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="inlineStr">
+        <is>
+          <t>% Alto o Muy alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Desarrollo profesional</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>92 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>Acceso a nuevas oportunidades laborales</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>77 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Capacidad para resolver problemas complejos</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>92 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>Desarrollo de capacidades de investigación</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D65" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>100 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Innovación y desarrollo tecnológico</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>92 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>Liderazgo de proyectos</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="11" t="inlineStr">
+        <is>
+          <t>69 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Toma de decisiones basada en información</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>92 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo interdisciplinario</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D69" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>92 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Desarrollo de redes académicas/profesionales</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>77 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>Continuación de estudios de formación avanzada</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D71" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="11" t="inlineStr">
+        <is>
+          <t>85 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Generación o transferencia de conocimiento</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>77 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Actividades después de graduarse (selección múltiple)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>Respuesta</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B75" s="10" t="inlineStr">
         <is>
           <t>Egresados</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C75" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>GIIRA</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Desarrollo de software o soluciones tecnológicas</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>85 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>Participación en grupos de investigación</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>77 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Participación en proyectos de investigación</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>69 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>Publicaciones científicas o académicas</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>69 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Docencia universitaria</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>62 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>Ponencias en eventos internacionales.</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>54 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Ponencias en eventos nacionales.</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>46 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>Dirección de trabajos de grado</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>46 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>Participación en proyectos con entidades públicas o privadas</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>46 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t>Participación en redes académicas o profesionales</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>38 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Patentes, registros de software u otros productos de propiedad intelectual</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>31 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t>Innovaciones o mejoras de procesos</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>27 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>INTECSE</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>27 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>GICOGE</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>23 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>Contribución en publicación de libro</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>9 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>GITEM++</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="n">
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>8 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t>Consultorías especializadas</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>9 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>PROPROBOS</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n">
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>8 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>Dirección o participación en proyectos de impacto social</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>9 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>GCEM</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>9 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>INTERNET INTELIGENTE</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>9 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Situación principal actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>8 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Formación continuada después de graduarse (selección múltiple)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="10" t="inlineStr">
         <is>
           <t>Respuesta</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B93" s="10" t="inlineStr">
         <is>
           <t>Egresados</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C93" s="10" t="inlineStr">
         <is>
           <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Docente</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>36 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>Empleado(a)</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>36 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Independiente/consultor(a)</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>18 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>Estudiante</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>9 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Sector en el que se desempeña</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>Respuesta</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>Egresados</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Educación Superior</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>45 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>Gobierno/sector público</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>27 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>TIC</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>9 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>9 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Industria</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>9 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Nivel de responsabilidad del cargo</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>Respuesta</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>Egresados</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Profesional/especialista</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>36 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>Docencia</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C47" s="11" t="inlineStr">
-        <is>
-          <t>36 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>Dirección/jefatura</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>9 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>Coordinación</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>9 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Investigación</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>9 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Relación de la actividad actual con la formación recibida</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>Respuesta</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>Egresados</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Totalmente Relacionada</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>64 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>Parcialmente relacionada</t>
-        </is>
-      </c>
-      <c r="B55" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C55" s="11" t="inlineStr">
-        <is>
-          <t>18 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>Muy Relacionada</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>9 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>Poco relacionada</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" s="11" t="inlineStr">
-        <is>
-          <t>9 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Aporte de la MCIC a su desarrollo (número de egresados por nivel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="10" t="inlineStr">
-        <is>
-          <t>Dimensión</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="inlineStr">
-        <is>
-          <t>Muy alto</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
-        <is>
-          <t>Alto</t>
-        </is>
-      </c>
-      <c r="D60" s="10" t="inlineStr">
-        <is>
-          <t>Medio</t>
-        </is>
-      </c>
-      <c r="E60" s="10" t="inlineStr">
-        <is>
-          <t>Bajo</t>
-        </is>
-      </c>
-      <c r="F60" s="10" t="inlineStr">
-        <is>
-          <t>Ningún aporte</t>
-        </is>
-      </c>
-      <c r="G60" s="10" t="inlineStr">
-        <is>
-          <t>% Alto o Muy alto</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>Desarrollo profesional</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="C61" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D61" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>91 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t>Acceso a nuevas oportunidades laborales</t>
-        </is>
-      </c>
-      <c r="B62" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="C62" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E62" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="11" t="inlineStr">
-        <is>
-          <t>73 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>Capacidad para resolver problemas complejos</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C63" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>91 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="11" t="inlineStr">
-        <is>
-          <t>Desarrollo de capacidades de investigación</t>
-        </is>
-      </c>
-      <c r="B64" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="C64" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D64" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="11" t="inlineStr">
-        <is>
-          <t>100 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>Innovación y desarrollo tecnológico</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="C65" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>91 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>Liderazgo de proyectos</t>
-        </is>
-      </c>
-      <c r="B66" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C66" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D66" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E66" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" s="11" t="inlineStr">
-        <is>
-          <t>64 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>Toma de decisiones basada en información</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C67" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D67" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>91 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t>Trabajo interdisciplinario</t>
-        </is>
-      </c>
-      <c r="B68" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="C68" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D68" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F68" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="11" t="inlineStr">
-        <is>
-          <t>91 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>Desarrollo de redes académicas/profesionales</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C69" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D69" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F69" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>73 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t>Continuación de estudios de formación avanzada</t>
-        </is>
-      </c>
-      <c r="B70" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C70" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D70" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="11" t="inlineStr">
-        <is>
-          <t>82 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>Generación o transferencia de conocimiento</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C71" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D71" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>82 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>Actividades después de graduarse (selección múltiple)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="10" t="inlineStr">
-        <is>
-          <t>Respuesta</t>
-        </is>
-      </c>
-      <c r="B74" s="10" t="inlineStr">
-        <is>
-          <t>Egresados</t>
-        </is>
-      </c>
-      <c r="C74" s="10" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>Desarrollo de software o soluciones tecnológicas</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>82 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t>Participación en grupos de investigación</t>
-        </is>
-      </c>
-      <c r="B76" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="C76" s="11" t="inlineStr">
-        <is>
-          <t>73 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>Participación en proyectos de investigación</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>64 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t>Publicaciones científicas o académicas</t>
-        </is>
-      </c>
-      <c r="B78" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="C78" s="11" t="inlineStr">
-        <is>
-          <t>64 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>Docencia universitaria</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>55 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="11" t="inlineStr">
-        <is>
-          <t>Ponencias en eventos internacionales.</t>
-        </is>
-      </c>
-      <c r="B80" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C80" s="11" t="inlineStr">
-        <is>
-          <t>55 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>Ponencias en eventos nacionales.</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>45 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="11" t="inlineStr">
-        <is>
-          <t>Participación en proyectos con entidades públicas o privadas</t>
-        </is>
-      </c>
-      <c r="B82" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C82" s="11" t="inlineStr">
-        <is>
-          <t>45 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>Dirección de trabajos de grado</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>36 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="11" t="inlineStr">
-        <is>
-          <t>Patentes, registros de software u otros productos de propiedad intelectual</t>
-        </is>
-      </c>
-      <c r="B84" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C84" s="11" t="inlineStr">
-        <is>
-          <t>27 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>Participación en redes académicas o profesionales</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>27 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="11" t="inlineStr">
-        <is>
-          <t>Innovaciones o mejoras de procesos</t>
-        </is>
-      </c>
-      <c r="B86" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C86" s="11" t="inlineStr">
-        <is>
-          <t>27 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>Contribución en publicación de libro</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>9 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="11" t="inlineStr">
-        <is>
-          <t>Consultorías especializadas</t>
-        </is>
-      </c>
-      <c r="B88" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C88" s="11" t="inlineStr">
-        <is>
-          <t>9 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>Formación continuada después de graduarse (selección múltiple)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="30" customHeight="1">
-      <c r="A91" s="10" t="inlineStr">
-        <is>
-          <t>Respuesta</t>
-        </is>
-      </c>
-      <c r="B91" s="10" t="inlineStr">
-        <is>
-          <t>Egresados</t>
-        </is>
-      </c>
-      <c r="C91" s="10" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>36 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="11" t="inlineStr">
-        <is>
-          <t>Doctorado</t>
-        </is>
-      </c>
-      <c r="B93" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C93" s="11" t="inlineStr">
-        <is>
-          <t>36 %</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>Curso / diplomados</t>
+          <t>No</t>
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>18 %</t>
+          <t>38 %</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>38 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>Curso / diplomados</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>15 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
           <t>Otra Maestría</t>
         </is>
       </c>
-      <c r="B95" s="11" t="n">
+      <c r="B97" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C95" s="11" t="inlineStr">
-        <is>
-          <t>9 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>8 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>Pertenece o ha pertenecido a un grupo de investigación</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="10" t="inlineStr">
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="10" t="inlineStr">
         <is>
           <t>Respuesta</t>
         </is>
       </c>
-      <c r="B98" s="10" t="inlineStr">
+      <c r="B100" s="10" t="inlineStr">
         <is>
           <t>Egresados</t>
         </is>
       </c>
-      <c r="C98" s="10" t="inlineStr">
+      <c r="C100" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>73 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B100" s="11" t="n">
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>77 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C100" s="11" t="inlineStr">
-        <is>
-          <t>27 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>23 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>Ha publicado productos académicos o científicos después de graduarse</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="30" customHeight="1">
-      <c r="A103" s="10" t="inlineStr">
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" s="10" t="inlineStr">
         <is>
           <t>Respuesta</t>
         </is>
       </c>
-      <c r="B103" s="10" t="inlineStr">
+      <c r="B105" s="10" t="inlineStr">
         <is>
           <t>Egresados</t>
         </is>
       </c>
-      <c r="C103" s="10" t="inlineStr">
+      <c r="C105" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>73 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B105" s="11" t="n">
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>77 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C105" s="11" t="inlineStr">
-        <is>
-          <t>27 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>23 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>Valoración de la formación (escala 1 a 5)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="30" customHeight="1">
-      <c r="A108" s="10" t="inlineStr">
+    <row r="110" ht="30" customHeight="1">
+      <c r="A110" s="10" t="inlineStr">
         <is>
           <t>Aspecto</t>
         </is>
       </c>
-      <c r="B108" s="10" t="inlineStr">
+      <c r="B110" s="10" t="inlineStr">
         <is>
           <t>Promedio</t>
         </is>
       </c>
-      <c r="C108" s="10" t="inlineStr">
+      <c r="C110" s="10" t="inlineStr">
         <is>
           <t>Respuestas</t>
         </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>Pertinencia de la formación recibida</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="C109" s="6" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="11" t="inlineStr">
-        <is>
-          <t>Actualidad de los conocimientos adquiridos</t>
-        </is>
-      </c>
-      <c r="B110" s="11" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="C110" s="11" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>Contribución de la Maestría a su desempeño profesional</t>
+          <t>Pertinencia de la formación recibida</t>
         </is>
       </c>
       <c r="B111" s="6" t="n">
-        <v>4.55</v>
+        <v>4.46</v>
       </c>
       <c r="C111" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>Contribución a sus capacidades investigativas</t>
+          <t>Actualidad de los conocimientos adquiridos</t>
         </is>
       </c>
       <c r="B112" s="11" t="n">
-        <v>4.64</v>
+        <v>4.31</v>
       </c>
       <c r="C112" s="11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>Contribución a su capacidad de innovación</t>
+          <t>Contribución de la Maestría a su desempeño profesional</t>
         </is>
       </c>
       <c r="B113" s="6" t="n">
-        <v>4.45</v>
+        <v>4.31</v>
       </c>
       <c r="C113" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>Reconocimiento de la MCIC en su entorno profesional</t>
+          <t>Contribución a sus capacidades investigativas</t>
         </is>
       </c>
       <c r="B114" s="11" t="n">
-        <v>3.91</v>
+        <v>4.69</v>
       </c>
       <c r="C114" s="11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
+          <t>Contribución a su capacidad de innovación</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="C115" s="6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>Reconocimiento de la MCIC en su entorno profesional</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C116" s="11" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
           <t>Correspondencia entre la formación recibida y las necesidades actuales del entorno</t>
         </is>
       </c>
-      <c r="B115" s="6" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="C115" s="6" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="3" t="inlineStr">
+      <c r="B117" s="6" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="C117" s="6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
         <is>
           <t>¿Recomendaría la MCIC a otros profesionales?</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="30" customHeight="1">
-      <c r="A118" s="10" t="inlineStr">
+    <row r="120" ht="30" customHeight="1">
+      <c r="A120" s="10" t="inlineStr">
         <is>
           <t>Respuesta</t>
         </is>
       </c>
-      <c r="B118" s="10" t="inlineStr">
+      <c r="B120" s="10" t="inlineStr">
         <is>
           <t>Egresados</t>
         </is>
       </c>
-      <c r="C118" s="10" t="inlineStr">
+      <c r="C120" s="10" t="inlineStr">
         <is>
           <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>Probablemente sí</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>55 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="11" t="inlineStr">
-        <is>
-          <t>Definitivamente sí</t>
-        </is>
-      </c>
-      <c r="B120" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C120" s="11" t="inlineStr">
-        <is>
-          <t>36 %</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
+          <t>Definitivamente sí</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>46 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>Probablemente sí</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C122" s="11" t="inlineStr">
+        <is>
+          <t>46 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
           <t>Probablemente no</t>
         </is>
       </c>
-      <c r="B121" s="6" t="n">
+      <c r="B123" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>9 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="3" t="inlineStr">
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>8 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
         <is>
           <t>¿Ha generado algún impacto en su entorno a partir de su formación?</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="30" customHeight="1">
-      <c r="A124" s="10" t="inlineStr">
+    <row r="126" ht="30" customHeight="1">
+      <c r="A126" s="10" t="inlineStr">
         <is>
           <t>Respuesta</t>
         </is>
       </c>
-      <c r="B124" s="10" t="inlineStr">
+      <c r="B126" s="10" t="inlineStr">
         <is>
           <t>Egresados</t>
         </is>
       </c>
-      <c r="C124" s="10" t="inlineStr">
+      <c r="C126" s="10" t="inlineStr">
         <is>
           <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>64 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="11" t="inlineStr">
-        <is>
-          <t>Parcialmente</t>
-        </is>
-      </c>
-      <c r="B126" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C126" s="11" t="inlineStr">
-        <is>
-          <t>18 %</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B127" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>62 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>Parcialmente</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C128" s="11" t="inlineStr">
+        <is>
+          <t>23 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>18 %</t>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>15 %</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A45:H45"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A92:H92"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A109:H109"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A125:H125"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A107:H107"/>
-    <mergeCell ref="A117:H117"/>
-    <mergeCell ref="A90:H90"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A104:H104"/>
+    <mergeCell ref="A99:H99"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A102:H102"/>
-    <mergeCell ref="A123:H123"/>
-    <mergeCell ref="A97:H97"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A119:H119"/>
+    <mergeCell ref="A74:H74"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
